--- a/results/supplementary/Supplementary_Table_S5_chronomic_gene_catalogue.xlsx
+++ b/results/supplementary/Supplementary_Table_S5_chronomic_gene_catalogue.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>One row per Mendelian disease gene in a chronotype locus (r2 &gt;= 0.6 interval): diseases, inheritance, ClinGen class, HPO phenotype flags, nearest gene and Open Targets L2G status, MAGMA gene p, exome burden p and direction (Backman et al. 2021), QTL colocalisation tissues, gnomAD v2.1.1 LOEUF, mouse circadian atlas and GTEx day-night expression. evidence_count = number of five gene-level evidence lines, which are not independent: L2G &gt;= 0.5 for the gene in a credible set at the locus (ev_l2g; l2g_gene_score = the gene's highest L2G score at the locus; l2g_gene/l2g_score = the top L2G gene at the locus), nearest gene to the lead (ev_nearest), MAGMA Bonferroni (ev_magma), exome burden p &lt; 0.01 (ev_burden), QTL colocalisation with eCAVIAR CLPP &gt;= 0.1 (ev_qtl; qtl_max_clpp gives the largest CLPP &gt;= 0.01).</t>
+          <t>One row per Mendelian disease gene in a chronotype locus (r2 &gt;= 0.6 interval): diseases, inheritance, ClinGen class, HPO phenotype flags, nearest gene and Open Targets L2G status, MAGMA gene p, exome burden p and direction (Backman et al. 2021), QTL colocalisation tissues, gnomAD v2.1.1 LoF constraint (LOEUF_v2; descriptive only), mouse circadian atlas and GTEx day-night expression. evidence_count = number of five gene-level evidence lines, which are not independent: L2G &gt;= 0.5 for the gene in a credible set at the locus (ev_l2g; l2g_gene_score = the gene's highest L2G score at the locus; l2g_gene/l2g_score = the top L2G gene at the locus), nearest gene to the lead (ev_nearest), MAGMA Bonferroni (ev_magma), exome burden p &lt; 0.01 (ev_burden), QTL colocalisation with eCAVIAR CLPP &gt;= 0.1 (ev_qtl; qtl_max_clpp gives the largest CLPP &gt;= 0.01).</t>
         </is>
       </c>
     </row>
